--- a/ru/downloads/data-excel/2.2.3.1.xlsx
+++ b/ru/downloads/data-excel/2.2.3.1.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC57EF7-1A48-4A52-BA9D-090FE244F55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20370" windowHeight="11790"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2.2.3" sheetId="2" r:id="rId1"/>
+    <sheet name="2.2.3.1" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -30,9 +31,6 @@
   </si>
   <si>
     <t xml:space="preserve">  дети 0- 14 лет</t>
-  </si>
-  <si>
-    <t>2.2.3 Доля женщин с анемией к общей численности населения</t>
   </si>
   <si>
     <t>15 лет и старше</t>
@@ -62,9 +60,6 @@
     <t>Доля беременных женщин, страдающих анемией к численности женщин, закончивших беременность</t>
   </si>
   <si>
-    <t xml:space="preserve">Доля женщин, зарегистрированных случаев заболеваний анемией </t>
-  </si>
-  <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
   <si>
@@ -72,15 +67,6 @@
   </si>
   <si>
     <t>Items</t>
-  </si>
-  <si>
-    <t>2.2.3 Анемия менен ооруган аялдардын калктын жалпы санындагы үлүшү</t>
-  </si>
-  <si>
-    <t>Аз кандуулук менен ооруган аялдардын үлүшү</t>
-  </si>
-  <si>
-    <t>Percentage of women with reported cases of anemia</t>
   </si>
   <si>
     <t>including:</t>
@@ -176,13 +162,28 @@
     <t>Osh city</t>
   </si>
   <si>
-    <t>2.2.3 Proportion of women with anemia to the total population</t>
+    <t>2.2.3.1 Доля женщин с анемией к общей численности женщин</t>
+  </si>
+  <si>
+    <t>2.2.3.1 Анемиясы бар аялдардын үлүшү жалпы аялдардын санына карата</t>
+  </si>
+  <si>
+    <t>2.2.3.1 Proportion of women with anaemia among the total female population</t>
+  </si>
+  <si>
+    <t>Доля женщин с анемией к общей численности женщин</t>
+  </si>
+  <si>
+    <t>Proportion of women with anaemia among the total female population</t>
+  </si>
+  <si>
+    <t>Анемиясы бар аялдардын үлүшү жалпы аялдардын санына карата</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -366,7 +367,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -392,17 +393,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -414,25 +408,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -441,14 +435,11 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -456,10 +447,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normal 17" xfId="2"/>
-    <cellStyle name="Normal 3 2" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -475,7 +466,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -7852,9 +7843,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7892,9 +7883,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7929,7 +7920,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7964,7 +7955,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8137,54 +8128,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="36.85546875" style="12" customWidth="1"/>
-    <col min="4" max="13" width="9.140625" style="12"/>
-    <col min="14" max="14" width="12" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="3" width="36.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
+        <v>47</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="25" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="8">
         <v>2015</v>
@@ -8212,56 +8201,62 @@
       </c>
       <c r="L3" s="8">
         <v>2023</v>
+      </c>
+      <c r="M3" s="8">
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="F4" s="3">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="G4" s="3">
-        <v>2.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H4" s="4">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="5">
-        <v>1.1560222744136313</v>
-      </c>
-      <c r="J4" s="24">
-        <v>1.3</v>
-      </c>
-      <c r="K4" s="24">
-        <v>1.7</v>
-      </c>
-      <c r="L4" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="N4" s="26"/>
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="K4" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="L4" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="M4" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>19</v>
+      <c r="C5" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -8269,497 +8264,533 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="N5" s="26"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="N5" s="23"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="7">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="E6" s="7">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="F6" s="7">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="7">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="H6" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="I6" s="10">
-        <v>1.2576108982867509</v>
-      </c>
-      <c r="J6" s="25">
         <v>1.5</v>
       </c>
-      <c r="K6" s="25">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L6" s="25">
-        <v>1.9</v>
-      </c>
-      <c r="N6" s="26"/>
+      <c r="I6" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="J6" s="22">
+        <v>1</v>
+      </c>
+      <c r="K6" s="22">
+        <v>1.4</v>
+      </c>
+      <c r="L6" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="M6" s="22">
+        <v>0.9</v>
+      </c>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="9">
-        <v>3.2</v>
-      </c>
-      <c r="E7" s="9">
-        <v>2.6</v>
-      </c>
-      <c r="F7" s="9">
-        <v>2.6</v>
-      </c>
-      <c r="G7" s="9">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1.8</v>
-      </c>
-      <c r="I7" s="13">
-        <v>1.1083522735584705</v>
-      </c>
-      <c r="J7" s="25">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="E7" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K7" s="25">
-        <v>1.4</v>
-      </c>
-      <c r="L7" s="25">
-        <v>1.2</v>
-      </c>
-      <c r="N7" s="26"/>
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="J7" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="22">
+        <v>0.6</v>
+      </c>
+      <c r="L7" s="22">
+        <v>0.6</v>
+      </c>
+      <c r="M7" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="L8" s="12">
-        <v>39</v>
-      </c>
+      <c r="A8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="18">
+      <c r="A9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="15">
         <v>52.846005311752421</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="15">
         <v>47.502069193842075</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="15">
         <v>52.792095035969247</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="15">
         <v>58.958872780326232</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="15">
         <v>55.240236953305867</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="15">
         <v>40.422042571724099</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="21">
         <v>35.440295222940719</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="21">
         <v>41.1</v>
       </c>
-      <c r="L9" s="24"/>
+      <c r="L9" s="21">
+        <v>39</v>
+      </c>
+      <c r="M9" s="21">
+        <v>31</v>
+      </c>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="20">
+      <c r="A10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="17">
         <v>93.343001173952075</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="17">
         <v>63.42195540308748</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="17">
         <v>87.940428623320017</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="17">
         <v>86.9164265129683</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="17">
         <v>88.203209234477072</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="17">
         <v>62.073018438257542</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="22">
         <v>59.171812568107519</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="22">
         <v>65.90209110066462</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="22">
         <v>49.967045641786129</v>
+      </c>
+      <c r="M10" s="22">
+        <v>32.01567261645625</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="20">
+      <c r="A11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="17">
         <v>69.843444897399891</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="17">
         <v>56.804051694027244</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="17">
         <v>70.58142898466879</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="17">
         <v>75.097679886587599</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="17">
         <v>80.273802115743621</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="17">
         <v>59.732990300038246</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="22">
         <v>44.777330673249253</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="22">
         <v>55.941036331149498</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="22">
         <v>43.247229681176961</v>
+      </c>
+      <c r="M11" s="22">
+        <v>35.486459378134406</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="20">
+      <c r="A12" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="17">
         <v>33.221509620128273</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="17">
         <v>35.099337748344375</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="17">
         <v>39.201903319995672</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="17">
         <v>31.307684330602509</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="17">
         <v>26.755677039529012</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="17">
         <v>29.473684210526311</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="22">
         <v>23.062381852551987</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="22">
         <v>21.263715474839199</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="22">
         <v>25.20876826722338</v>
+      </c>
+      <c r="M12" s="22">
+        <v>18.59920033089756</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="20">
+      <c r="A13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="17">
         <v>37.077865266841648</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="17">
         <v>34.445603058741746</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="17">
         <v>32.450331125827816</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="17">
         <v>27.505407354001441</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="17">
         <v>20.346732710992573</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="17">
         <v>18.726591760299627</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="22">
         <v>19.815313582146977</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="22">
         <v>11.351981351981353</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="22">
         <v>15.235173824130879</v>
+      </c>
+      <c r="M13" s="22">
+        <v>15.507169410515134</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="20">
+      <c r="A14" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="17">
         <v>40.599510603588904</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="17">
         <v>43.986527862829149</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="17">
         <v>49.77569915052019</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="17">
         <v>49.038739102823165</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="17">
         <v>46.766805472932774</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="17">
         <v>25.552099054424492</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="22">
         <v>23.537217999758717</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="22">
         <v>32.279274699203526</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="22">
         <v>36.397123311699701</v>
+      </c>
+      <c r="M14" s="22">
+        <v>26.08352378973613</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="20">
+      <c r="A15" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="17">
         <v>48.794449262792718</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="17">
         <v>61.884873796985651</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="17">
         <v>51.555882894494566</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="17">
         <v>39.738874586244947</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="17">
         <v>32.170099160945838</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="17">
         <v>41.943974431284076</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="22">
         <v>33.438661710037174</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="22">
         <v>36.890901250539024</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="22">
         <v>32.449725776965266</v>
+      </c>
+      <c r="M15" s="22">
+        <v>25.190294957183635</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="17">
+        <v>31.488781817296928</v>
+      </c>
+      <c r="E16" s="17">
+        <v>34.041943343046867</v>
+      </c>
+      <c r="F16" s="17">
+        <v>31.154507740564608</v>
+      </c>
+      <c r="G16" s="17">
+        <v>35.764418675617939</v>
+      </c>
+      <c r="H16" s="17">
+        <v>30.102889212221989</v>
+      </c>
+      <c r="I16" s="17">
+        <v>24.779419581162966</v>
+      </c>
+      <c r="J16" s="22">
+        <v>27.234744365035734</v>
+      </c>
+      <c r="K16" s="22">
+        <v>32.421298573536646</v>
+      </c>
+      <c r="L16" s="22">
+        <v>30.303402530401669</v>
+      </c>
+      <c r="M16" s="22">
+        <v>30.240992987829451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="17">
+        <v>67.903553299492387</v>
+      </c>
+      <c r="E17" s="17">
+        <v>53.621316494450824</v>
+      </c>
+      <c r="F17" s="17">
+        <v>54.348249975626409</v>
+      </c>
+      <c r="G17" s="17">
+        <v>99.421992262154475</v>
+      </c>
+      <c r="H17" s="17">
+        <v>61.361069277108435</v>
+      </c>
+      <c r="I17" s="17">
+        <v>47.93962264150943</v>
+      </c>
+      <c r="J17" s="22">
+        <v>42.607395183332471</v>
+      </c>
+      <c r="K17" s="22">
+        <v>43.227712137486577</v>
+      </c>
+      <c r="L17" s="22">
+        <v>50.286734473057784</v>
+      </c>
+      <c r="M17" s="22">
+        <v>39.880440197454824</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="20">
-        <v>31.488781817296928</v>
-      </c>
-      <c r="E16" s="20">
-        <v>34.041943343046867</v>
-      </c>
-      <c r="F16" s="20">
-        <v>31.154507740564608</v>
-      </c>
-      <c r="G16" s="20">
-        <v>35.764418675617939</v>
-      </c>
-      <c r="H16" s="20">
-        <v>30.102889212221989</v>
-      </c>
-      <c r="I16" s="20">
-        <v>24.779419581162966</v>
-      </c>
-      <c r="J16" s="25">
-        <v>27.234744365035734</v>
-      </c>
-      <c r="K16" s="25">
-        <v>32.421298573536646</v>
-      </c>
-      <c r="L16" s="25">
-        <v>30.303402530401669</v>
+      <c r="D18" s="19">
+        <v>38.72057795385691</v>
+      </c>
+      <c r="E18" s="19">
+        <v>48.088623579382386</v>
+      </c>
+      <c r="F18" s="19">
+        <v>41.182821497120919</v>
+      </c>
+      <c r="G18" s="19">
+        <v>31.186184293457707</v>
+      </c>
+      <c r="H18" s="19">
+        <v>32.093395902483692</v>
+      </c>
+      <c r="I18" s="19">
+        <v>38.133333333333333</v>
+      </c>
+      <c r="J18" s="20">
+        <v>34.332723948811697</v>
+      </c>
+      <c r="K18" s="26">
+        <v>38.737482570668021</v>
+      </c>
+      <c r="L18" s="26">
+        <v>37.055296469020654</v>
+      </c>
+      <c r="M18" s="26">
+        <v>27.303252885624346</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="20">
-        <v>67.903553299492387</v>
-      </c>
-      <c r="E17" s="20">
-        <v>53.621316494450824</v>
-      </c>
-      <c r="F17" s="20">
-        <v>54.348249975626409</v>
-      </c>
-      <c r="G17" s="20">
-        <v>99.421992262154475</v>
-      </c>
-      <c r="H17" s="20">
-        <v>61.361069277108435</v>
-      </c>
-      <c r="I17" s="20">
-        <v>47.93962264150943</v>
-      </c>
-      <c r="J17" s="25">
-        <v>42.607395183332471</v>
-      </c>
-      <c r="K17" s="25">
-        <v>43.227712137486577</v>
-      </c>
-      <c r="L17" s="25">
-        <v>50.286734473057784</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="22">
-        <v>38.72057795385691</v>
-      </c>
-      <c r="E18" s="22">
-        <v>48.088623579382386</v>
-      </c>
-      <c r="F18" s="22">
-        <v>41.182821497120919</v>
-      </c>
-      <c r="G18" s="22">
-        <v>31.186184293457707</v>
-      </c>
-      <c r="H18" s="22">
-        <v>32.093395902483692</v>
-      </c>
-      <c r="I18" s="22">
-        <v>38.133333333333333</v>
-      </c>
-      <c r="J18" s="23">
-        <v>34.332723948811697</v>
-      </c>
-      <c r="K18" s="30">
-        <v>38.737482570668021</v>
-      </c>
-      <c r="L18" s="30">
-        <v>37.055296469020654</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
